--- a/data/trans_dic/P25A$rendimiento-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,49</t>
+          <t>1,96; 6,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,79</t>
+          <t>1,18; 5,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,01</t>
+          <t>2,93; 8,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,52</t>
+          <t>0,0; 14,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,82</t>
+          <t>0,0; 10,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,61</t>
+          <t>0,0; 14,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,12</t>
+          <t>2,08; 5,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,86</t>
+          <t>1,37; 4,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,1</t>
+          <t>2,7; 8,21</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,54</t>
+          <t>1,2; 5,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,08</t>
+          <t>3,05; 7,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,51</t>
+          <t>2,33; 7,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,63</t>
+          <t>1,83; 9,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,72</t>
+          <t>0,74; 6,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,66</t>
+          <t>2,49; 8,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,56</t>
+          <t>1,87; 5,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,82</t>
+          <t>2,52; 5,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,79</t>
+          <t>2,96; 6,75</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,67</t>
+          <t>0,89; 7,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 14,47</t>
+          <t>2,17; 13,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 18,89</t>
+          <t>1,81; 17,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 13,93</t>
+          <t>1,4; 13,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,28</t>
+          <t>2,16; 12,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,35</t>
+          <t>2,02; 9,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,99</t>
+          <t>1,76; 8,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,7</t>
+          <t>3,07; 9,95</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,88</t>
+          <t>2,06; 4,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,24</t>
+          <t>2,54; 5,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,22</t>
+          <t>3,48; 7,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,42</t>
+          <t>2,77; 8,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,66</t>
+          <t>1,69; 5,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,69</t>
+          <t>2,78; 7,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,01</t>
+          <t>2,65; 5,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,84</t>
+          <t>2,56; 4,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,51</t>
+          <t>3,72; 6,5</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6336; 19658</t>
+          <t>5937; 18474</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4087; 17833</t>
+          <t>4406; 18612</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5861; 18914</t>
+          <t>6145; 18080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6510</t>
+          <t>0; 7140</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6786</t>
+          <t>0; 7096</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4369</t>
+          <t>0; 5304</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7609; 21509</t>
+          <t>7292; 20610</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6268; 21426</t>
+          <t>6050; 21059</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6750; 20034</t>
+          <t>6684; 20319</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2807; 13137</t>
+          <t>2837; 13378</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11253; 28087</t>
+          <t>10608; 27169</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7529; 22693</t>
+          <t>7043; 22281</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2862; 13046</t>
+          <t>2763; 13626</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1295; 13725</t>
+          <t>1776; 14812</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5111; 17418</t>
+          <t>5007; 17409</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7446; 21604</t>
+          <t>7263; 21255</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14348; 34213</t>
+          <t>14789; 34948</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15136; 34161</t>
+          <t>14912; 33960</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6417</t>
+          <t>0; 6214</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>860; 8342</t>
+          <t>854; 7571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1932; 12964</t>
+          <t>1945; 12475</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1150; 9700</t>
+          <t>932; 9054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1840; 10782</t>
+          <t>1084; 10505</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2017; 11677</t>
+          <t>2056; 11442</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2688; 11345</t>
+          <t>2744; 12570</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3153; 13873</t>
+          <t>3056; 15346</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5580; 19754</t>
+          <t>5666; 18368</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13128; 30466</t>
+          <t>12841; 29474</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19923; 42768</t>
+          <t>20728; 43390</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20385; 43442</t>
+          <t>20920; 43763</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7348; 21121</t>
+          <t>6940; 21806</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6864; 21879</t>
+          <t>6521; 20973</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9840; 25657</t>
+          <t>9269; 25349</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23317; 43831</t>
+          <t>23224; 43983</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30754; 58175</t>
+          <t>30736; 57019</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35388; 60879</t>
+          <t>34781; 60749</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$rendimiento-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,1</t>
+          <t>2,07; 6,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,0</t>
+          <t>1,09; 4,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,62</t>
+          <t>2,89; 8,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,83</t>
+          <t>0,0; 13,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,27</t>
+          <t>0,0; 9,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,1</t>
+          <t>0,0; 11,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,87</t>
+          <t>2,1; 5,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,77</t>
+          <t>1,3; 4,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,21</t>
+          <t>2,77; 8,4</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,64</t>
+          <t>1,2; 5,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,81</t>
+          <t>3,16; 7,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,38</t>
+          <t>2,4; 7,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 9,01</t>
+          <t>1,86; 8,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,17</t>
+          <t>0,52; 5,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,66</t>
+          <t>2,43; 8,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,47</t>
+          <t>1,98; 5,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,95</t>
+          <t>2,56; 5,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,75</t>
+          <t>2,95; 6,93</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,87</t>
+          <t>0,92; 8,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 13,92</t>
+          <t>2,15; 15,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 17,63</t>
+          <t>1,85; 18,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 13,57</t>
+          <t>2,45; 14,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,04</t>
+          <t>2,07; 11,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,26</t>
+          <t>1,53; 8,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,84</t>
+          <t>2,14; 8,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,95</t>
+          <t>3,01; 10,5</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,72</t>
+          <t>2,09; 4,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,32</t>
+          <t>2,63; 5,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,28</t>
+          <t>3,49; 7,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,7</t>
+          <t>2,81; 8,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,43</t>
+          <t>1,87; 5,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,59</t>
+          <t>2,95; 7,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,02</t>
+          <t>2,61; 5,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,74</t>
+          <t>2,64; 4,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,5</t>
+          <t>3,61; 6,61</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5937; 18474</t>
+          <t>6262; 18749</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4406; 18612</t>
+          <t>4071; 18200</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6145; 18080</t>
+          <t>6060; 18226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7140</t>
+          <t>0; 6331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7096</t>
+          <t>0; 6688</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5304</t>
+          <t>0; 4316</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7292; 20610</t>
+          <t>7384; 20384</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6050; 21059</t>
+          <t>5726; 20614</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6684; 20319</t>
+          <t>6859; 20778</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2837; 13378</t>
+          <t>2844; 13249</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10608; 27169</t>
+          <t>10997; 26988</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7043; 22281</t>
+          <t>7263; 22007</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2763; 13626</t>
+          <t>2810; 13049</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1776; 14812</t>
+          <t>1258; 13061</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5007; 17409</t>
+          <t>4894; 17079</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7263; 21255</t>
+          <t>7669; 22154</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14789; 34948</t>
+          <t>15074; 34674</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14912; 33960</t>
+          <t>14850; 34843</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6214</t>
+          <t>0; 6498</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>854; 7571</t>
+          <t>886; 7868</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1945; 12475</t>
+          <t>1927; 13846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>932; 9054</t>
+          <t>948; 9461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1084; 10505</t>
+          <t>1897; 11051</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2056; 11442</t>
+          <t>1972; 11373</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2744; 12570</t>
+          <t>2081; 11625</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3056; 15346</t>
+          <t>3725; 14278</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5666; 18368</t>
+          <t>5562; 19400</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12841; 29474</t>
+          <t>13057; 30053</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20728; 43390</t>
+          <t>21455; 43465</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20920; 43763</t>
+          <t>20989; 42437</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6940; 21806</t>
+          <t>7051; 20533</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6521; 20973</t>
+          <t>7246; 23098</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9269; 25349</t>
+          <t>9844; 25373</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23224; 43983</t>
+          <t>22869; 44669</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30736; 57019</t>
+          <t>31715; 59310</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34781; 60749</t>
+          <t>33807; 61778</t>
         </is>
       </c>
     </row>
